--- a/数据/原始数据/股指期货信号.xlsx
+++ b/数据/原始数据/股指期货信号.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aa\WorkBuddy\2026-05-28-14-41-45\huatai-risk-parity-replication\数据\原始数据\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A540B939-F1C3-48AA-B9B0-B9107A31A308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32B64DBC-DA20-481E-9EC4-8F517EBDA12A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4872" yWindow="-17388" windowWidth="30936" windowHeight="16776" xr2:uid="{AE3579B6-3A12-4CC8-B539-9B068F69DB99}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AE3579B6-3A12-4CC8-B539-9B068F69DB99}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -437,7 +437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EC48170-C128-4AC2-B848-964C5ACF2463}">
-  <dimension ref="A1:B2190"/>
+  <dimension ref="A1:B2206"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.5" style="1" customWidth="1"/>
@@ -17551,6 +17551,89 @@
         <v>46250</v>
       </c>
     </row>
+    <row r="2191" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2191" s="1">
+        <v>46251</v>
+      </c>
+    </row>
+    <row r="2192" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2192" s="1">
+        <v>46252</v>
+      </c>
+    </row>
+    <row r="2193" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2193" s="1">
+        <v>46253</v>
+      </c>
+    </row>
+    <row r="2194" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2194" s="1">
+        <v>46254</v>
+      </c>
+    </row>
+    <row r="2195" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2195" s="1">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="2196" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2196" s="1">
+        <v>46256</v>
+      </c>
+    </row>
+    <row r="2197" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2197" s="1">
+        <v>46257</v>
+      </c>
+    </row>
+    <row r="2198" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2198" s="1">
+        <v>46258</v>
+      </c>
+    </row>
+    <row r="2199" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2199" s="1">
+        <v>46259</v>
+      </c>
+    </row>
+    <row r="2200" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2200" s="1">
+        <v>46260</v>
+      </c>
+    </row>
+    <row r="2201" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2201" s="1">
+        <v>46261</v>
+      </c>
+      <c r="B2201" s="3">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="2202" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2202" s="1">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="2203" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2203" s="1">
+        <v>46263</v>
+      </c>
+    </row>
+    <row r="2204" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2204" s="1">
+        <v>46264</v>
+      </c>
+    </row>
+    <row r="2205" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2205" s="1">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="2206" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2206" s="1">
+        <v>46266</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
